--- a/apparel_order_forms/007_team_branded_accessory_order_form--apparel_order_forms.xlsx
+++ b/apparel_order_forms/007_team_branded_accessory_order_form--apparel_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'water_bottle'}</t>
+          <t>water_bottle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Water Bottle'}</t>
+          <t>Water Bottle</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'t-shirt'}</t>
+          <t>t-shirt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'T-Shirt'}</t>
+          <t>T-Shirt</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hat'}</t>
+          <t>hat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hat'}</t>
+          <t>Hat</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-store_pickup'}</t>
+          <t>in-store_pickup</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-Store Pickup'}</t>
+          <t>In-Store Pickup</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
